--- a/data/Processed/ECF_smartphone_survey.xlsx
+++ b/data/Processed/ECF_smartphone_survey.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ecf-exp2-notif-mmn\data\Processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FB15B19-0BF8-451F-9BC2-1DCD9BC3E6DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A38A49F0-3800-41ED-8D91-AD283233D8CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3977" uniqueCount="771">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4100" uniqueCount="811">
   <si>
     <t>Pragya Verma</t>
   </si>
@@ -2351,6 +2351,126 @@
   <si>
     <t>iitd</t>
   </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>3/13/2025 17:21:03</t>
+  </si>
+  <si>
+    <t>bristid25@gmail.com</t>
+  </si>
+  <si>
+    <t>SD048</t>
+  </si>
+  <si>
+    <t>3/15/2025 16:58:59</t>
+  </si>
+  <si>
+    <t>poulamisarkar343@gmail.com</t>
+  </si>
+  <si>
+    <t>SD049</t>
+  </si>
+  <si>
+    <t>3/16/2025 16:51:42</t>
+  </si>
+  <si>
+    <t>singhsaloni1808@gmail.com</t>
+  </si>
+  <si>
+    <t>Sd050</t>
+  </si>
+  <si>
+    <t>3/18/2025 17:51:45</t>
+  </si>
+  <si>
+    <t>lakipa1703@gmail.com</t>
+  </si>
+  <si>
+    <t>SD051</t>
+  </si>
+  <si>
+    <t>3/19/2025 15:43:31</t>
+  </si>
+  <si>
+    <t>chelsea.ml2001@gmail.com</t>
+  </si>
+  <si>
+    <t>SD052</t>
+  </si>
+  <si>
+    <t>3/21/2025 15:51:59</t>
+  </si>
+  <si>
+    <t>chesta3110@gmail.com</t>
+  </si>
+  <si>
+    <t>SD053</t>
+  </si>
+  <si>
+    <t>3/21/2025 20:01:29</t>
+  </si>
+  <si>
+    <t>natashaoberoi6988@gmail.com</t>
+  </si>
+  <si>
+    <t>Sd054</t>
+  </si>
+  <si>
+    <t>3/27/2025 12:19:19</t>
+  </si>
+  <si>
+    <t>bachwankuldeep@gmail.com</t>
+  </si>
+  <si>
+    <t>SD055</t>
+  </si>
+  <si>
+    <t>3/30/2025 13:55:55</t>
+  </si>
+  <si>
+    <t>gaurishankar91490@gmail.com</t>
+  </si>
+  <si>
+    <t>SD056</t>
+  </si>
+  <si>
+    <t>3/30/2025 18:08:46</t>
+  </si>
+  <si>
+    <t>ankitmathurmohammadi@gmail.com</t>
+  </si>
+  <si>
+    <t>SD057</t>
+  </si>
+  <si>
+    <t>3/30/2025 20:50:27</t>
+  </si>
+  <si>
+    <t>prataprajsingh6@gmail.com</t>
+  </si>
+  <si>
+    <t>Sd058</t>
+  </si>
+  <si>
+    <t>3/30/2025 23:17:51</t>
+  </si>
+  <si>
+    <t>SD059</t>
+  </si>
+  <si>
+    <t>rahulenviitd@gmail.com</t>
+  </si>
+  <si>
+    <t>SD060</t>
+  </si>
+  <si>
+    <t>kumarikiran58147@gmail.com</t>
+  </si>
+  <si>
+    <t>SD061</t>
+  </si>
 </sst>
 </file>
 
@@ -2586,7 +2706,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -2629,6 +2749,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2844,7 +2965,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27FE39DF-3F10-4BBA-BDE5-4E31BDACBA24}">
-  <dimension ref="A1:CF331"/>
+  <dimension ref="A1:CF345"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.28515625" customWidth="1"/>
@@ -2854,6 +2975,12 @@
     <col min="5" max="5" width="15.140625" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
     <col min="7" max="7" width="16.5703125" customWidth="1"/>
+    <col min="69" max="69" width="17.42578125" customWidth="1"/>
+    <col min="70" max="71" width="14.28515625" customWidth="1"/>
+    <col min="72" max="72" width="18.7109375" customWidth="1"/>
+    <col min="73" max="73" width="15.5703125" customWidth="1"/>
+    <col min="74" max="74" width="12.140625" customWidth="1"/>
+    <col min="75" max="75" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:84" x14ac:dyDescent="0.2">
@@ -3071,7 +3198,7 @@
         <v>206</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>207</v>
+        <v>771</v>
       </c>
       <c r="BU1" s="1" t="s">
         <v>208</v>
@@ -80277,6 +80404,3097 @@
         <v>127</v>
       </c>
     </row>
+    <row r="332" spans="1:84" x14ac:dyDescent="0.2">
+      <c r="A332" t="s">
+        <v>772</v>
+      </c>
+      <c r="B332" t="s">
+        <v>773</v>
+      </c>
+      <c r="C332" t="s">
+        <v>774</v>
+      </c>
+      <c r="H332">
+        <v>5</v>
+      </c>
+      <c r="I332">
+        <v>9</v>
+      </c>
+      <c r="J332">
+        <v>7</v>
+      </c>
+      <c r="K332">
+        <v>10</v>
+      </c>
+      <c r="L332">
+        <v>8</v>
+      </c>
+      <c r="M332">
+        <v>9</v>
+      </c>
+      <c r="N332">
+        <v>1</v>
+      </c>
+      <c r="O332">
+        <v>2</v>
+      </c>
+      <c r="P332">
+        <v>7</v>
+      </c>
+      <c r="Q332">
+        <v>7</v>
+      </c>
+      <c r="R332">
+        <v>7</v>
+      </c>
+      <c r="S332">
+        <v>7</v>
+      </c>
+      <c r="T332">
+        <v>8</v>
+      </c>
+      <c r="U332">
+        <v>8</v>
+      </c>
+      <c r="V332">
+        <v>2</v>
+      </c>
+      <c r="W332">
+        <v>7</v>
+      </c>
+      <c r="X332">
+        <v>10</v>
+      </c>
+      <c r="Y332">
+        <v>9</v>
+      </c>
+      <c r="Z332">
+        <v>2</v>
+      </c>
+      <c r="AA332">
+        <v>8</v>
+      </c>
+      <c r="AB332">
+        <v>7</v>
+      </c>
+      <c r="AC332">
+        <v>1</v>
+      </c>
+      <c r="AD332">
+        <v>4</v>
+      </c>
+      <c r="AE332">
+        <v>6</v>
+      </c>
+      <c r="AF332">
+        <v>2</v>
+      </c>
+      <c r="AG332">
+        <v>9</v>
+      </c>
+      <c r="AH332">
+        <v>7</v>
+      </c>
+      <c r="AI332">
+        <v>2</v>
+      </c>
+      <c r="AJ332">
+        <v>4</v>
+      </c>
+      <c r="AK332">
+        <v>4</v>
+      </c>
+      <c r="AL332">
+        <v>3</v>
+      </c>
+      <c r="AM332">
+        <v>5</v>
+      </c>
+      <c r="AN332">
+        <v>4</v>
+      </c>
+      <c r="AO332">
+        <v>2</v>
+      </c>
+      <c r="AP332">
+        <v>2</v>
+      </c>
+      <c r="AQ332">
+        <v>5</v>
+      </c>
+      <c r="AR332">
+        <v>1</v>
+      </c>
+      <c r="AS332">
+        <v>2</v>
+      </c>
+      <c r="AT332">
+        <v>2</v>
+      </c>
+      <c r="AU332">
+        <v>1</v>
+      </c>
+      <c r="AV332">
+        <v>1</v>
+      </c>
+      <c r="AW332">
+        <v>3</v>
+      </c>
+      <c r="AX332">
+        <v>3</v>
+      </c>
+      <c r="AY332">
+        <v>2</v>
+      </c>
+      <c r="AZ332">
+        <v>2</v>
+      </c>
+      <c r="BA332">
+        <v>3</v>
+      </c>
+      <c r="BB332">
+        <v>2</v>
+      </c>
+      <c r="BC332">
+        <v>1</v>
+      </c>
+      <c r="BD332">
+        <v>3</v>
+      </c>
+      <c r="BE332">
+        <v>2</v>
+      </c>
+      <c r="BF332">
+        <v>1</v>
+      </c>
+      <c r="BG332">
+        <v>3</v>
+      </c>
+      <c r="BH332">
+        <v>2</v>
+      </c>
+      <c r="BI332">
+        <v>5</v>
+      </c>
+      <c r="BJ332">
+        <v>4</v>
+      </c>
+      <c r="BK332">
+        <v>5</v>
+      </c>
+      <c r="BL332">
+        <v>4</v>
+      </c>
+      <c r="BM332">
+        <v>4</v>
+      </c>
+      <c r="BN332">
+        <v>6</v>
+      </c>
+      <c r="BO332">
+        <v>4</v>
+      </c>
+      <c r="BP332" t="s">
+        <v>219</v>
+      </c>
+      <c r="BQ332" t="s">
+        <v>222</v>
+      </c>
+      <c r="BR332" t="s">
+        <v>225</v>
+      </c>
+      <c r="BS332" t="s">
+        <v>222</v>
+      </c>
+      <c r="BT332" t="s">
+        <v>117</v>
+      </c>
+      <c r="BU332" t="s">
+        <v>218</v>
+      </c>
+      <c r="BV332">
+        <v>2</v>
+      </c>
+      <c r="BW332">
+        <v>4</v>
+      </c>
+      <c r="CE332">
+        <v>169</v>
+      </c>
+      <c r="CF332">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="333" spans="1:84" x14ac:dyDescent="0.2">
+      <c r="A333" t="s">
+        <v>775</v>
+      </c>
+      <c r="B333" t="s">
+        <v>776</v>
+      </c>
+      <c r="C333" t="s">
+        <v>777</v>
+      </c>
+      <c r="H333">
+        <v>1</v>
+      </c>
+      <c r="I333">
+        <v>8</v>
+      </c>
+      <c r="J333">
+        <v>8</v>
+      </c>
+      <c r="K333">
+        <v>10</v>
+      </c>
+      <c r="L333">
+        <v>3</v>
+      </c>
+      <c r="M333">
+        <v>6</v>
+      </c>
+      <c r="N333">
+        <v>2</v>
+      </c>
+      <c r="O333">
+        <v>2</v>
+      </c>
+      <c r="P333">
+        <v>7</v>
+      </c>
+      <c r="Q333">
+        <v>5</v>
+      </c>
+      <c r="R333">
+        <v>8</v>
+      </c>
+      <c r="S333">
+        <v>7</v>
+      </c>
+      <c r="T333">
+        <v>1</v>
+      </c>
+      <c r="U333">
+        <v>6</v>
+      </c>
+      <c r="V333">
+        <v>1</v>
+      </c>
+      <c r="W333">
+        <v>4</v>
+      </c>
+      <c r="X333">
+        <v>9</v>
+      </c>
+      <c r="Y333">
+        <v>7</v>
+      </c>
+      <c r="Z333">
+        <v>2</v>
+      </c>
+      <c r="AA333">
+        <v>8</v>
+      </c>
+      <c r="AB333">
+        <v>9</v>
+      </c>
+      <c r="AC333">
+        <v>2</v>
+      </c>
+      <c r="AD333">
+        <v>4</v>
+      </c>
+      <c r="AE333">
+        <v>5</v>
+      </c>
+      <c r="AF333">
+        <v>6</v>
+      </c>
+      <c r="AG333">
+        <v>1</v>
+      </c>
+      <c r="AH333">
+        <v>5</v>
+      </c>
+      <c r="AI333">
+        <v>1</v>
+      </c>
+      <c r="AJ333">
+        <v>4</v>
+      </c>
+      <c r="AK333">
+        <v>2</v>
+      </c>
+      <c r="AL333">
+        <v>5</v>
+      </c>
+      <c r="AM333">
+        <v>5</v>
+      </c>
+      <c r="AN333">
+        <v>5</v>
+      </c>
+      <c r="AO333">
+        <v>3</v>
+      </c>
+      <c r="AP333">
+        <v>4</v>
+      </c>
+      <c r="AQ333">
+        <v>4</v>
+      </c>
+      <c r="AR333">
+        <v>3</v>
+      </c>
+      <c r="AS333">
+        <v>2</v>
+      </c>
+      <c r="AT333">
+        <v>3</v>
+      </c>
+      <c r="AU333">
+        <v>4</v>
+      </c>
+      <c r="AV333">
+        <v>2</v>
+      </c>
+      <c r="AW333">
+        <v>3</v>
+      </c>
+      <c r="AX333">
+        <v>1</v>
+      </c>
+      <c r="AY333">
+        <v>1</v>
+      </c>
+      <c r="AZ333">
+        <v>4</v>
+      </c>
+      <c r="BA333">
+        <v>5</v>
+      </c>
+      <c r="BB333">
+        <v>4</v>
+      </c>
+      <c r="BC333">
+        <v>2</v>
+      </c>
+      <c r="BD333">
+        <v>3</v>
+      </c>
+      <c r="BE333">
+        <v>1</v>
+      </c>
+      <c r="BF333">
+        <v>3</v>
+      </c>
+      <c r="BG333">
+        <v>5</v>
+      </c>
+      <c r="BH333">
+        <v>2</v>
+      </c>
+      <c r="BI333">
+        <v>5</v>
+      </c>
+      <c r="BJ333">
+        <v>5</v>
+      </c>
+      <c r="BK333">
+        <v>5</v>
+      </c>
+      <c r="BL333">
+        <v>4</v>
+      </c>
+      <c r="BM333">
+        <v>5</v>
+      </c>
+      <c r="BN333">
+        <v>5</v>
+      </c>
+      <c r="BO333">
+        <v>4</v>
+      </c>
+      <c r="BP333" t="s">
+        <v>219</v>
+      </c>
+      <c r="BQ333" t="s">
+        <v>222</v>
+      </c>
+      <c r="BR333" t="s">
+        <v>222</v>
+      </c>
+      <c r="BS333" t="s">
+        <v>225</v>
+      </c>
+      <c r="BT333" t="s">
+        <v>117</v>
+      </c>
+      <c r="BU333" t="s">
+        <v>224</v>
+      </c>
+      <c r="BV333">
+        <v>1</v>
+      </c>
+      <c r="BW333">
+        <v>3</v>
+      </c>
+      <c r="CE333">
+        <v>137</v>
+      </c>
+      <c r="CF333">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="334" spans="1:84" x14ac:dyDescent="0.2">
+      <c r="A334" t="s">
+        <v>778</v>
+      </c>
+      <c r="B334" t="s">
+        <v>779</v>
+      </c>
+      <c r="C334" t="s">
+        <v>780</v>
+      </c>
+      <c r="H334">
+        <v>7</v>
+      </c>
+      <c r="I334">
+        <v>8</v>
+      </c>
+      <c r="J334">
+        <v>5</v>
+      </c>
+      <c r="K334">
+        <v>10</v>
+      </c>
+      <c r="L334">
+        <v>2</v>
+      </c>
+      <c r="M334">
+        <v>7</v>
+      </c>
+      <c r="N334">
+        <v>7</v>
+      </c>
+      <c r="O334">
+        <v>9</v>
+      </c>
+      <c r="P334">
+        <v>9</v>
+      </c>
+      <c r="Q334">
+        <v>7</v>
+      </c>
+      <c r="R334">
+        <v>6</v>
+      </c>
+      <c r="S334">
+        <v>7</v>
+      </c>
+      <c r="T334">
+        <v>1</v>
+      </c>
+      <c r="U334">
+        <v>5</v>
+      </c>
+      <c r="V334">
+        <v>5</v>
+      </c>
+      <c r="W334">
+        <v>6</v>
+      </c>
+      <c r="X334">
+        <v>4</v>
+      </c>
+      <c r="Y334">
+        <v>7</v>
+      </c>
+      <c r="Z334">
+        <v>6</v>
+      </c>
+      <c r="AA334">
+        <v>6</v>
+      </c>
+      <c r="AB334">
+        <v>7</v>
+      </c>
+      <c r="AC334">
+        <v>7</v>
+      </c>
+      <c r="AD334">
+        <v>4</v>
+      </c>
+      <c r="AE334">
+        <v>7</v>
+      </c>
+      <c r="AF334">
+        <v>8</v>
+      </c>
+      <c r="AG334">
+        <v>5</v>
+      </c>
+      <c r="AH334">
+        <v>1</v>
+      </c>
+      <c r="AI334">
+        <v>3</v>
+      </c>
+      <c r="AJ334">
+        <v>3</v>
+      </c>
+      <c r="AK334">
+        <v>4</v>
+      </c>
+      <c r="AL334">
+        <v>4</v>
+      </c>
+      <c r="AM334">
+        <v>5</v>
+      </c>
+      <c r="AN334">
+        <v>3</v>
+      </c>
+      <c r="AO334">
+        <v>4</v>
+      </c>
+      <c r="AP334">
+        <v>5</v>
+      </c>
+      <c r="AQ334">
+        <v>5</v>
+      </c>
+      <c r="AR334">
+        <v>5</v>
+      </c>
+      <c r="AS334">
+        <v>4</v>
+      </c>
+      <c r="AT334">
+        <v>3</v>
+      </c>
+      <c r="AU334">
+        <v>4</v>
+      </c>
+      <c r="AV334">
+        <v>3</v>
+      </c>
+      <c r="AW334">
+        <v>3</v>
+      </c>
+      <c r="AX334">
+        <v>4</v>
+      </c>
+      <c r="AY334">
+        <v>4</v>
+      </c>
+      <c r="AZ334">
+        <v>5</v>
+      </c>
+      <c r="BA334">
+        <v>5</v>
+      </c>
+      <c r="BB334">
+        <v>5</v>
+      </c>
+      <c r="BC334">
+        <v>4</v>
+      </c>
+      <c r="BD334">
+        <v>4</v>
+      </c>
+      <c r="BE334">
+        <v>5</v>
+      </c>
+      <c r="BF334">
+        <v>5</v>
+      </c>
+      <c r="BG334">
+        <v>4</v>
+      </c>
+      <c r="BH334">
+        <v>5</v>
+      </c>
+      <c r="BI334">
+        <v>4</v>
+      </c>
+      <c r="BJ334">
+        <v>5</v>
+      </c>
+      <c r="BK334">
+        <v>4</v>
+      </c>
+      <c r="BL334">
+        <v>5</v>
+      </c>
+      <c r="BM334">
+        <v>4</v>
+      </c>
+      <c r="BN334">
+        <v>4</v>
+      </c>
+      <c r="BO334">
+        <v>4</v>
+      </c>
+      <c r="BP334" t="s">
+        <v>216</v>
+      </c>
+      <c r="BQ334" t="s">
+        <v>220</v>
+      </c>
+      <c r="BR334" t="s">
+        <v>222</v>
+      </c>
+      <c r="BS334" t="s">
+        <v>222</v>
+      </c>
+      <c r="BT334" t="s">
+        <v>116</v>
+      </c>
+      <c r="BU334" t="s">
+        <v>218</v>
+      </c>
+      <c r="BV334">
+        <v>3</v>
+      </c>
+      <c r="BW334">
+        <v>3</v>
+      </c>
+      <c r="CE334">
+        <v>163</v>
+      </c>
+      <c r="CF334">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="335" spans="1:84" x14ac:dyDescent="0.2">
+      <c r="A335" t="s">
+        <v>781</v>
+      </c>
+      <c r="B335" t="s">
+        <v>782</v>
+      </c>
+      <c r="C335" t="s">
+        <v>783</v>
+      </c>
+      <c r="H335">
+        <v>8</v>
+      </c>
+      <c r="I335">
+        <v>8</v>
+      </c>
+      <c r="J335">
+        <v>8</v>
+      </c>
+      <c r="K335">
+        <v>10</v>
+      </c>
+      <c r="L335">
+        <v>9</v>
+      </c>
+      <c r="M335">
+        <v>9</v>
+      </c>
+      <c r="N335">
+        <v>1</v>
+      </c>
+      <c r="O335">
+        <v>1</v>
+      </c>
+      <c r="P335">
+        <v>5</v>
+      </c>
+      <c r="Q335">
+        <v>7</v>
+      </c>
+      <c r="R335">
+        <v>8</v>
+      </c>
+      <c r="S335">
+        <v>8</v>
+      </c>
+      <c r="T335">
+        <v>7</v>
+      </c>
+      <c r="U335">
+        <v>5</v>
+      </c>
+      <c r="V335">
+        <v>1</v>
+      </c>
+      <c r="W335">
+        <v>4</v>
+      </c>
+      <c r="X335">
+        <v>4</v>
+      </c>
+      <c r="Y335">
+        <v>7</v>
+      </c>
+      <c r="Z335">
+        <v>5</v>
+      </c>
+      <c r="AA335">
+        <v>9</v>
+      </c>
+      <c r="AB335">
+        <v>8</v>
+      </c>
+      <c r="AC335">
+        <v>1</v>
+      </c>
+      <c r="AD335">
+        <v>1</v>
+      </c>
+      <c r="AE335">
+        <v>3</v>
+      </c>
+      <c r="AF335">
+        <v>1</v>
+      </c>
+      <c r="AG335">
+        <v>4</v>
+      </c>
+      <c r="AH335">
+        <v>3</v>
+      </c>
+      <c r="AI335">
+        <v>3</v>
+      </c>
+      <c r="AJ335">
+        <v>5</v>
+      </c>
+      <c r="AK335">
+        <v>4</v>
+      </c>
+      <c r="AL335">
+        <v>4</v>
+      </c>
+      <c r="AM335">
+        <v>5</v>
+      </c>
+      <c r="AN335">
+        <v>4</v>
+      </c>
+      <c r="AO335">
+        <v>5</v>
+      </c>
+      <c r="AP335">
+        <v>4</v>
+      </c>
+      <c r="AQ335">
+        <v>4</v>
+      </c>
+      <c r="AR335">
+        <v>3</v>
+      </c>
+      <c r="AS335">
+        <v>4</v>
+      </c>
+      <c r="AT335">
+        <v>4</v>
+      </c>
+      <c r="AU335">
+        <v>4</v>
+      </c>
+      <c r="AV335">
+        <v>4</v>
+      </c>
+      <c r="AW335">
+        <v>4</v>
+      </c>
+      <c r="AX335">
+        <v>3</v>
+      </c>
+      <c r="AY335">
+        <v>4</v>
+      </c>
+      <c r="AZ335">
+        <v>4</v>
+      </c>
+      <c r="BA335">
+        <v>5</v>
+      </c>
+      <c r="BB335">
+        <v>2</v>
+      </c>
+      <c r="BC335">
+        <v>2</v>
+      </c>
+      <c r="BD335">
+        <v>2</v>
+      </c>
+      <c r="BE335">
+        <v>1</v>
+      </c>
+      <c r="BF335">
+        <v>2</v>
+      </c>
+      <c r="BG335">
+        <v>1</v>
+      </c>
+      <c r="BH335">
+        <v>1</v>
+      </c>
+      <c r="BI335">
+        <v>4</v>
+      </c>
+      <c r="BJ335">
+        <v>4</v>
+      </c>
+      <c r="BK335">
+        <v>4</v>
+      </c>
+      <c r="BL335">
+        <v>3</v>
+      </c>
+      <c r="BM335">
+        <v>5</v>
+      </c>
+      <c r="BN335">
+        <v>6</v>
+      </c>
+      <c r="BO335">
+        <v>3</v>
+      </c>
+      <c r="BP335" t="s">
+        <v>217</v>
+      </c>
+      <c r="BQ335" t="s">
+        <v>221</v>
+      </c>
+      <c r="BR335" t="s">
+        <v>220</v>
+      </c>
+      <c r="BS335" t="s">
+        <v>222</v>
+      </c>
+      <c r="BT335" t="s">
+        <v>117</v>
+      </c>
+      <c r="BU335" t="s">
+        <v>224</v>
+      </c>
+      <c r="BV335">
+        <v>2</v>
+      </c>
+      <c r="BW335">
+        <v>3</v>
+      </c>
+      <c r="CE335">
+        <v>145</v>
+      </c>
+      <c r="CF335">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="336" spans="1:84" x14ac:dyDescent="0.2">
+      <c r="A336" t="s">
+        <v>784</v>
+      </c>
+      <c r="B336" t="s">
+        <v>785</v>
+      </c>
+      <c r="C336" t="s">
+        <v>786</v>
+      </c>
+      <c r="H336">
+        <v>1</v>
+      </c>
+      <c r="I336">
+        <v>7</v>
+      </c>
+      <c r="J336">
+        <v>9</v>
+      </c>
+      <c r="K336">
+        <v>10</v>
+      </c>
+      <c r="L336">
+        <v>1</v>
+      </c>
+      <c r="M336">
+        <v>6</v>
+      </c>
+      <c r="N336">
+        <v>1</v>
+      </c>
+      <c r="O336">
+        <v>4</v>
+      </c>
+      <c r="P336">
+        <v>4</v>
+      </c>
+      <c r="Q336">
+        <v>4</v>
+      </c>
+      <c r="R336">
+        <v>3</v>
+      </c>
+      <c r="S336">
+        <v>4</v>
+      </c>
+      <c r="T336">
+        <v>4</v>
+      </c>
+      <c r="U336">
+        <v>2</v>
+      </c>
+      <c r="V336">
+        <v>1</v>
+      </c>
+      <c r="W336">
+        <v>3</v>
+      </c>
+      <c r="X336">
+        <v>3</v>
+      </c>
+      <c r="Y336">
+        <v>3</v>
+      </c>
+      <c r="Z336">
+        <v>5</v>
+      </c>
+      <c r="AA336">
+        <v>5</v>
+      </c>
+      <c r="AB336">
+        <v>5</v>
+      </c>
+      <c r="AC336">
+        <v>2</v>
+      </c>
+      <c r="AD336">
+        <v>3</v>
+      </c>
+      <c r="AE336">
+        <v>2</v>
+      </c>
+      <c r="AF336">
+        <v>1</v>
+      </c>
+      <c r="AG336">
+        <v>1</v>
+      </c>
+      <c r="AH336">
+        <v>3</v>
+      </c>
+      <c r="AI336">
+        <v>2</v>
+      </c>
+      <c r="AJ336">
+        <v>5</v>
+      </c>
+      <c r="AK336">
+        <v>4</v>
+      </c>
+      <c r="AL336">
+        <v>4</v>
+      </c>
+      <c r="AM336">
+        <v>3</v>
+      </c>
+      <c r="AN336">
+        <v>2</v>
+      </c>
+      <c r="AO336">
+        <v>2</v>
+      </c>
+      <c r="AP336">
+        <v>5</v>
+      </c>
+      <c r="AQ336">
+        <v>3</v>
+      </c>
+      <c r="AR336">
+        <v>1</v>
+      </c>
+      <c r="AS336">
+        <v>2</v>
+      </c>
+      <c r="AT336">
+        <v>2</v>
+      </c>
+      <c r="AU336">
+        <v>1</v>
+      </c>
+      <c r="AV336">
+        <v>5</v>
+      </c>
+      <c r="AW336">
+        <v>2</v>
+      </c>
+      <c r="AX336">
+        <v>2</v>
+      </c>
+      <c r="AY336">
+        <v>1</v>
+      </c>
+      <c r="AZ336">
+        <v>5</v>
+      </c>
+      <c r="BA336">
+        <v>1</v>
+      </c>
+      <c r="BB336">
+        <v>2</v>
+      </c>
+      <c r="BC336">
+        <v>1</v>
+      </c>
+      <c r="BD336">
+        <v>3</v>
+      </c>
+      <c r="BE336">
+        <v>2</v>
+      </c>
+      <c r="BF336">
+        <v>1</v>
+      </c>
+      <c r="BG336">
+        <v>2</v>
+      </c>
+      <c r="BH336">
+        <v>2</v>
+      </c>
+      <c r="BI336">
+        <v>3</v>
+      </c>
+      <c r="BJ336">
+        <v>2</v>
+      </c>
+      <c r="BK336">
+        <v>4</v>
+      </c>
+      <c r="BL336">
+        <v>3</v>
+      </c>
+      <c r="BM336">
+        <v>2</v>
+      </c>
+      <c r="BN336">
+        <v>3</v>
+      </c>
+      <c r="BO336">
+        <v>2</v>
+      </c>
+      <c r="BP336" t="s">
+        <v>216</v>
+      </c>
+      <c r="BQ336" t="s">
+        <v>222</v>
+      </c>
+      <c r="BR336" t="s">
+        <v>220</v>
+      </c>
+      <c r="BS336" t="s">
+        <v>222</v>
+      </c>
+      <c r="BT336" t="s">
+        <v>117</v>
+      </c>
+      <c r="BU336" t="s">
+        <v>218</v>
+      </c>
+      <c r="BV336">
+        <v>4</v>
+      </c>
+      <c r="BW336">
+        <v>5</v>
+      </c>
+      <c r="CE336">
+        <v>97</v>
+      </c>
+      <c r="CF336">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="337" spans="1:84" x14ac:dyDescent="0.2">
+      <c r="A337" t="s">
+        <v>787</v>
+      </c>
+      <c r="B337" t="s">
+        <v>788</v>
+      </c>
+      <c r="C337" t="s">
+        <v>789</v>
+      </c>
+      <c r="H337">
+        <v>3</v>
+      </c>
+      <c r="I337">
+        <v>7</v>
+      </c>
+      <c r="J337">
+        <v>8</v>
+      </c>
+      <c r="K337">
+        <v>10</v>
+      </c>
+      <c r="L337">
+        <v>3</v>
+      </c>
+      <c r="M337">
+        <v>3</v>
+      </c>
+      <c r="N337">
+        <v>1</v>
+      </c>
+      <c r="O337">
+        <v>2</v>
+      </c>
+      <c r="P337">
+        <v>2</v>
+      </c>
+      <c r="Q337">
+        <v>2</v>
+      </c>
+      <c r="R337">
+        <v>4</v>
+      </c>
+      <c r="S337">
+        <v>4</v>
+      </c>
+      <c r="T337">
+        <v>3</v>
+      </c>
+      <c r="U337">
+        <v>2</v>
+      </c>
+      <c r="V337">
+        <v>1</v>
+      </c>
+      <c r="W337">
+        <v>2</v>
+      </c>
+      <c r="X337">
+        <v>1</v>
+      </c>
+      <c r="Y337">
+        <v>4</v>
+      </c>
+      <c r="Z337">
+        <v>3</v>
+      </c>
+      <c r="AA337">
+        <v>4</v>
+      </c>
+      <c r="AB337">
+        <v>3</v>
+      </c>
+      <c r="AC337">
+        <v>2</v>
+      </c>
+      <c r="AD337">
+        <v>1</v>
+      </c>
+      <c r="AE337">
+        <v>1</v>
+      </c>
+      <c r="AF337">
+        <v>1</v>
+      </c>
+      <c r="AG337">
+        <v>2</v>
+      </c>
+      <c r="AH337">
+        <v>3</v>
+      </c>
+      <c r="AI337">
+        <v>5</v>
+      </c>
+      <c r="AJ337">
+        <v>1</v>
+      </c>
+      <c r="AK337">
+        <v>3</v>
+      </c>
+      <c r="AL337">
+        <v>2</v>
+      </c>
+      <c r="AM337">
+        <v>2</v>
+      </c>
+      <c r="AN337">
+        <v>4</v>
+      </c>
+      <c r="AO337">
+        <v>4</v>
+      </c>
+      <c r="AP337">
+        <v>4</v>
+      </c>
+      <c r="AQ337">
+        <v>3</v>
+      </c>
+      <c r="AR337">
+        <v>2</v>
+      </c>
+      <c r="AS337">
+        <v>3</v>
+      </c>
+      <c r="AT337">
+        <v>3</v>
+      </c>
+      <c r="AU337">
+        <v>3</v>
+      </c>
+      <c r="AV337">
+        <v>3</v>
+      </c>
+      <c r="AW337">
+        <v>1</v>
+      </c>
+      <c r="AX337">
+        <v>2</v>
+      </c>
+      <c r="AY337">
+        <v>2</v>
+      </c>
+      <c r="AZ337">
+        <v>2</v>
+      </c>
+      <c r="BA337">
+        <v>1</v>
+      </c>
+      <c r="BB337">
+        <v>3</v>
+      </c>
+      <c r="BC337">
+        <v>2</v>
+      </c>
+      <c r="BD337">
+        <v>2</v>
+      </c>
+      <c r="BE337">
+        <v>2</v>
+      </c>
+      <c r="BF337">
+        <v>2</v>
+      </c>
+      <c r="BG337">
+        <v>2</v>
+      </c>
+      <c r="BH337">
+        <v>2</v>
+      </c>
+      <c r="BI337">
+        <v>2</v>
+      </c>
+      <c r="BJ337">
+        <v>2</v>
+      </c>
+      <c r="BK337">
+        <v>2</v>
+      </c>
+      <c r="BL337">
+        <v>2</v>
+      </c>
+      <c r="BM337">
+        <v>2</v>
+      </c>
+      <c r="BN337">
+        <v>3</v>
+      </c>
+      <c r="BO337">
+        <v>2</v>
+      </c>
+      <c r="BP337" t="s">
+        <v>218</v>
+      </c>
+      <c r="BQ337" t="s">
+        <v>221</v>
+      </c>
+      <c r="BR337" t="s">
+        <v>221</v>
+      </c>
+      <c r="BS337" t="s">
+        <v>222</v>
+      </c>
+      <c r="BT337" t="s">
+        <v>117</v>
+      </c>
+      <c r="BU337" t="s">
+        <v>218</v>
+      </c>
+      <c r="BV337">
+        <v>1</v>
+      </c>
+      <c r="BW337">
+        <v>3</v>
+      </c>
+      <c r="CE337">
+        <v>82</v>
+      </c>
+      <c r="CF337">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="338" spans="1:84" x14ac:dyDescent="0.2">
+      <c r="A338" t="s">
+        <v>790</v>
+      </c>
+      <c r="B338" t="s">
+        <v>791</v>
+      </c>
+      <c r="C338" t="s">
+        <v>792</v>
+      </c>
+      <c r="H338">
+        <v>1</v>
+      </c>
+      <c r="I338">
+        <v>8</v>
+      </c>
+      <c r="J338">
+        <v>9</v>
+      </c>
+      <c r="K338">
+        <v>10</v>
+      </c>
+      <c r="L338">
+        <v>9</v>
+      </c>
+      <c r="M338">
+        <v>8</v>
+      </c>
+      <c r="N338">
+        <v>1</v>
+      </c>
+      <c r="O338">
+        <v>9</v>
+      </c>
+      <c r="P338">
+        <v>9</v>
+      </c>
+      <c r="Q338">
+        <v>9</v>
+      </c>
+      <c r="R338">
+        <v>3</v>
+      </c>
+      <c r="S338">
+        <v>5</v>
+      </c>
+      <c r="T338">
+        <v>1</v>
+      </c>
+      <c r="U338">
+        <v>3</v>
+      </c>
+      <c r="V338">
+        <v>1</v>
+      </c>
+      <c r="W338">
+        <v>7</v>
+      </c>
+      <c r="X338">
+        <v>7</v>
+      </c>
+      <c r="Y338">
+        <v>8</v>
+      </c>
+      <c r="Z338">
+        <v>9</v>
+      </c>
+      <c r="AA338">
+        <v>9</v>
+      </c>
+      <c r="AB338">
+        <v>9</v>
+      </c>
+      <c r="AC338">
+        <v>8</v>
+      </c>
+      <c r="AD338">
+        <v>3</v>
+      </c>
+      <c r="AE338">
+        <v>9</v>
+      </c>
+      <c r="AF338">
+        <v>9</v>
+      </c>
+      <c r="AG338">
+        <v>8</v>
+      </c>
+      <c r="AH338">
+        <v>5</v>
+      </c>
+      <c r="AI338">
+        <v>5</v>
+      </c>
+      <c r="AJ338">
+        <v>4</v>
+      </c>
+      <c r="AK338">
+        <v>5</v>
+      </c>
+      <c r="AL338">
+        <v>5</v>
+      </c>
+      <c r="AM338">
+        <v>5</v>
+      </c>
+      <c r="AN338">
+        <v>5</v>
+      </c>
+      <c r="AO338">
+        <v>5</v>
+      </c>
+      <c r="AP338">
+        <v>5</v>
+      </c>
+      <c r="AQ338">
+        <v>5</v>
+      </c>
+      <c r="AR338">
+        <v>4</v>
+      </c>
+      <c r="AS338">
+        <v>5</v>
+      </c>
+      <c r="AT338">
+        <v>5</v>
+      </c>
+      <c r="AU338">
+        <v>3</v>
+      </c>
+      <c r="AV338">
+        <v>5</v>
+      </c>
+      <c r="AW338">
+        <v>5</v>
+      </c>
+      <c r="AX338">
+        <v>4</v>
+      </c>
+      <c r="AY338">
+        <v>4</v>
+      </c>
+      <c r="AZ338">
+        <v>4</v>
+      </c>
+      <c r="BA338">
+        <v>4</v>
+      </c>
+      <c r="BB338">
+        <v>4</v>
+      </c>
+      <c r="BC338">
+        <v>4</v>
+      </c>
+      <c r="BD338">
+        <v>5</v>
+      </c>
+      <c r="BE338">
+        <v>4</v>
+      </c>
+      <c r="BF338">
+        <v>5</v>
+      </c>
+      <c r="BG338">
+        <v>5</v>
+      </c>
+      <c r="BH338">
+        <v>1</v>
+      </c>
+      <c r="BI338">
+        <v>4</v>
+      </c>
+      <c r="BJ338">
+        <v>3</v>
+      </c>
+      <c r="BK338">
+        <v>5</v>
+      </c>
+      <c r="BL338">
+        <v>5</v>
+      </c>
+      <c r="BM338">
+        <v>5</v>
+      </c>
+      <c r="BN338">
+        <v>5</v>
+      </c>
+      <c r="BO338">
+        <v>4</v>
+      </c>
+      <c r="BP338" t="s">
+        <v>219</v>
+      </c>
+      <c r="BQ338" t="s">
+        <v>221</v>
+      </c>
+      <c r="BR338" t="s">
+        <v>221</v>
+      </c>
+      <c r="BS338" t="s">
+        <v>222</v>
+      </c>
+      <c r="BT338" t="s">
+        <v>117</v>
+      </c>
+      <c r="BU338" t="s">
+        <v>224</v>
+      </c>
+      <c r="BV338">
+        <v>4</v>
+      </c>
+      <c r="BW338">
+        <v>3</v>
+      </c>
+      <c r="CE338">
+        <v>177</v>
+      </c>
+      <c r="CF338">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="339" spans="1:84" x14ac:dyDescent="0.2">
+      <c r="A339" t="s">
+        <v>793</v>
+      </c>
+      <c r="B339" t="s">
+        <v>794</v>
+      </c>
+      <c r="C339" t="s">
+        <v>795</v>
+      </c>
+      <c r="H339">
+        <v>6</v>
+      </c>
+      <c r="I339">
+        <v>9</v>
+      </c>
+      <c r="J339">
+        <v>3</v>
+      </c>
+      <c r="K339">
+        <v>10</v>
+      </c>
+      <c r="L339">
+        <v>2</v>
+      </c>
+      <c r="M339">
+        <v>2</v>
+      </c>
+      <c r="N339">
+        <v>3</v>
+      </c>
+      <c r="O339">
+        <v>7</v>
+      </c>
+      <c r="P339">
+        <v>7</v>
+      </c>
+      <c r="Q339">
+        <v>3</v>
+      </c>
+      <c r="R339">
+        <v>9</v>
+      </c>
+      <c r="S339">
+        <v>3</v>
+      </c>
+      <c r="T339">
+        <v>10</v>
+      </c>
+      <c r="U339">
+        <v>7</v>
+      </c>
+      <c r="V339">
+        <v>1</v>
+      </c>
+      <c r="W339">
+        <v>2</v>
+      </c>
+      <c r="X339">
+        <v>9</v>
+      </c>
+      <c r="Y339">
+        <v>2</v>
+      </c>
+      <c r="Z339">
+        <v>2</v>
+      </c>
+      <c r="AA339">
+        <v>8</v>
+      </c>
+      <c r="AB339">
+        <v>3</v>
+      </c>
+      <c r="AC339">
+        <v>3</v>
+      </c>
+      <c r="AD339">
+        <v>2</v>
+      </c>
+      <c r="AE339">
+        <v>1</v>
+      </c>
+      <c r="AF339">
+        <v>2</v>
+      </c>
+      <c r="AG339">
+        <v>7</v>
+      </c>
+      <c r="AH339">
+        <v>8</v>
+      </c>
+      <c r="AI339">
+        <v>1</v>
+      </c>
+      <c r="AJ339">
+        <v>2</v>
+      </c>
+      <c r="AK339">
+        <v>2</v>
+      </c>
+      <c r="AL339">
+        <v>1</v>
+      </c>
+      <c r="AM339">
+        <v>2</v>
+      </c>
+      <c r="AN339">
+        <v>6</v>
+      </c>
+      <c r="AO339">
+        <v>5</v>
+      </c>
+      <c r="AP339">
+        <v>5</v>
+      </c>
+      <c r="AQ339">
+        <v>4</v>
+      </c>
+      <c r="AR339">
+        <v>2</v>
+      </c>
+      <c r="AS339">
+        <v>5</v>
+      </c>
+      <c r="AT339">
+        <v>3</v>
+      </c>
+      <c r="AU339">
+        <v>4</v>
+      </c>
+      <c r="AV339">
+        <v>4</v>
+      </c>
+      <c r="AW339">
+        <v>5</v>
+      </c>
+      <c r="AX339">
+        <v>5</v>
+      </c>
+      <c r="AY339">
+        <v>1</v>
+      </c>
+      <c r="AZ339">
+        <v>5</v>
+      </c>
+      <c r="BA339">
+        <v>1</v>
+      </c>
+      <c r="BB339">
+        <v>5</v>
+      </c>
+      <c r="BC339">
+        <v>2</v>
+      </c>
+      <c r="BD339">
+        <v>5</v>
+      </c>
+      <c r="BE339">
+        <v>2</v>
+      </c>
+      <c r="BF339">
+        <v>5</v>
+      </c>
+      <c r="BG339">
+        <v>5</v>
+      </c>
+      <c r="BH339">
+        <v>2</v>
+      </c>
+      <c r="BI339">
+        <v>5</v>
+      </c>
+      <c r="BJ339">
+        <v>2</v>
+      </c>
+      <c r="BK339">
+        <v>5</v>
+      </c>
+      <c r="BL339">
+        <v>3</v>
+      </c>
+      <c r="BM339">
+        <v>2</v>
+      </c>
+      <c r="BN339">
+        <v>2</v>
+      </c>
+      <c r="BO339">
+        <v>2</v>
+      </c>
+      <c r="BP339" t="s">
+        <v>223</v>
+      </c>
+      <c r="BQ339" t="s">
+        <v>220</v>
+      </c>
+      <c r="BR339" t="s">
+        <v>225</v>
+      </c>
+      <c r="BS339" t="s">
+        <v>225</v>
+      </c>
+      <c r="BT339" t="s">
+        <v>117</v>
+      </c>
+      <c r="BU339" t="s">
+        <v>224</v>
+      </c>
+      <c r="BV339">
+        <v>2</v>
+      </c>
+      <c r="BW339">
+        <v>2</v>
+      </c>
+      <c r="CE339">
+        <v>131</v>
+      </c>
+      <c r="CF339">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="340" spans="1:84" x14ac:dyDescent="0.2">
+      <c r="A340" t="s">
+        <v>796</v>
+      </c>
+      <c r="B340" t="s">
+        <v>797</v>
+      </c>
+      <c r="C340" t="s">
+        <v>798</v>
+      </c>
+      <c r="H340">
+        <v>8</v>
+      </c>
+      <c r="I340">
+        <v>10</v>
+      </c>
+      <c r="J340">
+        <v>2</v>
+      </c>
+      <c r="K340">
+        <v>10</v>
+      </c>
+      <c r="L340">
+        <v>4</v>
+      </c>
+      <c r="M340">
+        <v>3</v>
+      </c>
+      <c r="N340">
+        <v>1</v>
+      </c>
+      <c r="O340">
+        <v>9</v>
+      </c>
+      <c r="P340">
+        <v>3</v>
+      </c>
+      <c r="Q340">
+        <v>2</v>
+      </c>
+      <c r="R340">
+        <v>8</v>
+      </c>
+      <c r="S340">
+        <v>9</v>
+      </c>
+      <c r="T340">
+        <v>8</v>
+      </c>
+      <c r="U340">
+        <v>8</v>
+      </c>
+      <c r="V340">
+        <v>1</v>
+      </c>
+      <c r="W340">
+        <v>3</v>
+      </c>
+      <c r="X340">
+        <v>8</v>
+      </c>
+      <c r="Y340">
+        <v>3</v>
+      </c>
+      <c r="Z340">
+        <v>2</v>
+      </c>
+      <c r="AA340">
+        <v>8</v>
+      </c>
+      <c r="AB340">
+        <v>8</v>
+      </c>
+      <c r="AC340">
+        <v>3</v>
+      </c>
+      <c r="AD340">
+        <v>8</v>
+      </c>
+      <c r="AE340">
+        <v>3</v>
+      </c>
+      <c r="AF340">
+        <v>8</v>
+      </c>
+      <c r="AG340">
+        <v>9</v>
+      </c>
+      <c r="AH340">
+        <v>9</v>
+      </c>
+      <c r="AI340">
+        <v>2</v>
+      </c>
+      <c r="AJ340">
+        <v>2</v>
+      </c>
+      <c r="AK340">
+        <v>3</v>
+      </c>
+      <c r="AL340">
+        <v>2</v>
+      </c>
+      <c r="AM340">
+        <v>2</v>
+      </c>
+      <c r="AN340">
+        <v>6</v>
+      </c>
+      <c r="AO340">
+        <v>6</v>
+      </c>
+      <c r="AP340">
+        <v>5</v>
+      </c>
+      <c r="AQ340">
+        <v>6</v>
+      </c>
+      <c r="AR340">
+        <v>5</v>
+      </c>
+      <c r="AS340">
+        <v>2</v>
+      </c>
+      <c r="AT340">
+        <v>1</v>
+      </c>
+      <c r="AU340">
+        <v>5</v>
+      </c>
+      <c r="AV340">
+        <v>5</v>
+      </c>
+      <c r="AW340">
+        <v>5</v>
+      </c>
+      <c r="AX340">
+        <v>5</v>
+      </c>
+      <c r="AY340">
+        <v>4</v>
+      </c>
+      <c r="AZ340">
+        <v>4</v>
+      </c>
+      <c r="BA340">
+        <v>1</v>
+      </c>
+      <c r="BB340">
+        <v>5</v>
+      </c>
+      <c r="BC340">
+        <v>5</v>
+      </c>
+      <c r="BD340">
+        <v>6</v>
+      </c>
+      <c r="BE340">
+        <v>5</v>
+      </c>
+      <c r="BF340">
+        <v>6</v>
+      </c>
+      <c r="BG340">
+        <v>6</v>
+      </c>
+      <c r="BH340">
+        <v>1</v>
+      </c>
+      <c r="BI340">
+        <v>6</v>
+      </c>
+      <c r="BJ340">
+        <v>5</v>
+      </c>
+      <c r="BK340">
+        <v>6</v>
+      </c>
+      <c r="BL340">
+        <v>5</v>
+      </c>
+      <c r="BM340">
+        <v>4</v>
+      </c>
+      <c r="BN340">
+        <v>5</v>
+      </c>
+      <c r="BO340">
+        <v>1</v>
+      </c>
+      <c r="BP340" t="s">
+        <v>218</v>
+      </c>
+      <c r="BQ340" t="s">
+        <v>220</v>
+      </c>
+      <c r="BR340" t="s">
+        <v>225</v>
+      </c>
+      <c r="BS340" t="s">
+        <v>225</v>
+      </c>
+      <c r="BT340" t="s">
+        <v>116</v>
+      </c>
+      <c r="BU340" t="s">
+        <v>224</v>
+      </c>
+      <c r="BV340">
+        <v>4</v>
+      </c>
+      <c r="BW340">
+        <v>2</v>
+      </c>
+      <c r="CE340">
+        <v>158</v>
+      </c>
+      <c r="CF340">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="341" spans="1:84" x14ac:dyDescent="0.2">
+      <c r="A341" t="s">
+        <v>799</v>
+      </c>
+      <c r="B341" t="s">
+        <v>800</v>
+      </c>
+      <c r="C341" t="s">
+        <v>801</v>
+      </c>
+      <c r="H341">
+        <v>6</v>
+      </c>
+      <c r="I341">
+        <v>8</v>
+      </c>
+      <c r="J341">
+        <v>9</v>
+      </c>
+      <c r="K341">
+        <v>10</v>
+      </c>
+      <c r="L341">
+        <v>8</v>
+      </c>
+      <c r="M341">
+        <v>8</v>
+      </c>
+      <c r="N341">
+        <v>2</v>
+      </c>
+      <c r="O341">
+        <v>3</v>
+      </c>
+      <c r="P341">
+        <v>3</v>
+      </c>
+      <c r="Q341">
+        <v>2</v>
+      </c>
+      <c r="R341">
+        <v>3</v>
+      </c>
+      <c r="S341">
+        <v>8</v>
+      </c>
+      <c r="T341">
+        <v>7</v>
+      </c>
+      <c r="U341">
+        <v>6</v>
+      </c>
+      <c r="V341">
+        <v>1</v>
+      </c>
+      <c r="W341">
+        <v>6</v>
+      </c>
+      <c r="X341">
+        <v>7</v>
+      </c>
+      <c r="Y341">
+        <v>8</v>
+      </c>
+      <c r="Z341">
+        <v>2</v>
+      </c>
+      <c r="AA341">
+        <v>4</v>
+      </c>
+      <c r="AB341">
+        <v>3</v>
+      </c>
+      <c r="AC341">
+        <v>2</v>
+      </c>
+      <c r="AD341">
+        <v>3</v>
+      </c>
+      <c r="AE341">
+        <v>4</v>
+      </c>
+      <c r="AF341">
+        <v>2</v>
+      </c>
+      <c r="AG341">
+        <v>9</v>
+      </c>
+      <c r="AH341">
+        <v>6</v>
+      </c>
+      <c r="AI341">
+        <v>2</v>
+      </c>
+      <c r="AJ341">
+        <v>2</v>
+      </c>
+      <c r="AK341">
+        <v>2</v>
+      </c>
+      <c r="AL341">
+        <v>2</v>
+      </c>
+      <c r="AM341">
+        <v>6</v>
+      </c>
+      <c r="AN341">
+        <v>4</v>
+      </c>
+      <c r="AO341">
+        <v>6</v>
+      </c>
+      <c r="AP341">
+        <v>4</v>
+      </c>
+      <c r="AQ341">
+        <v>3</v>
+      </c>
+      <c r="AR341">
+        <v>2</v>
+      </c>
+      <c r="AS341">
+        <v>2</v>
+      </c>
+      <c r="AT341">
+        <v>2</v>
+      </c>
+      <c r="AU341">
+        <v>2</v>
+      </c>
+      <c r="AV341">
+        <v>5</v>
+      </c>
+      <c r="AW341">
+        <v>5</v>
+      </c>
+      <c r="AX341">
+        <v>2</v>
+      </c>
+      <c r="AY341">
+        <v>2</v>
+      </c>
+      <c r="AZ341">
+        <v>5</v>
+      </c>
+      <c r="BA341">
+        <v>5</v>
+      </c>
+      <c r="BB341">
+        <v>3</v>
+      </c>
+      <c r="BC341">
+        <v>2</v>
+      </c>
+      <c r="BD341">
+        <v>2</v>
+      </c>
+      <c r="BE341">
+        <v>2</v>
+      </c>
+      <c r="BF341">
+        <v>2</v>
+      </c>
+      <c r="BG341">
+        <v>5</v>
+      </c>
+      <c r="BH341">
+        <v>2</v>
+      </c>
+      <c r="BI341">
+        <v>5</v>
+      </c>
+      <c r="BJ341">
+        <v>2</v>
+      </c>
+      <c r="BK341">
+        <v>2</v>
+      </c>
+      <c r="BL341">
+        <v>5</v>
+      </c>
+      <c r="BM341">
+        <v>2</v>
+      </c>
+      <c r="BN341">
+        <v>2</v>
+      </c>
+      <c r="BO341">
+        <v>2</v>
+      </c>
+      <c r="BP341" t="s">
+        <v>216</v>
+      </c>
+      <c r="BQ341" t="s">
+        <v>220</v>
+      </c>
+      <c r="BR341" t="s">
+        <v>220</v>
+      </c>
+      <c r="BS341" t="s">
+        <v>225</v>
+      </c>
+      <c r="BT341" t="s">
+        <v>117</v>
+      </c>
+      <c r="BU341" t="s">
+        <v>218</v>
+      </c>
+      <c r="BV341">
+        <v>3</v>
+      </c>
+      <c r="BW341">
+        <v>5</v>
+      </c>
+      <c r="CE341">
+        <v>140</v>
+      </c>
+      <c r="CF341">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="342" spans="1:84" x14ac:dyDescent="0.2">
+      <c r="A342" t="s">
+        <v>802</v>
+      </c>
+      <c r="B342" t="s">
+        <v>803</v>
+      </c>
+      <c r="C342" t="s">
+        <v>804</v>
+      </c>
+      <c r="H342">
+        <v>4</v>
+      </c>
+      <c r="I342">
+        <v>10</v>
+      </c>
+      <c r="J342">
+        <v>8</v>
+      </c>
+      <c r="K342">
+        <v>10</v>
+      </c>
+      <c r="L342">
+        <v>2</v>
+      </c>
+      <c r="M342">
+        <v>9</v>
+      </c>
+      <c r="N342">
+        <v>4</v>
+      </c>
+      <c r="O342">
+        <v>4</v>
+      </c>
+      <c r="P342">
+        <v>8</v>
+      </c>
+      <c r="Q342">
+        <v>2</v>
+      </c>
+      <c r="R342">
+        <v>3</v>
+      </c>
+      <c r="S342">
+        <v>9</v>
+      </c>
+      <c r="T342">
+        <v>9</v>
+      </c>
+      <c r="U342">
+        <v>3</v>
+      </c>
+      <c r="V342">
+        <v>1</v>
+      </c>
+      <c r="W342">
+        <v>2</v>
+      </c>
+      <c r="X342">
+        <v>9</v>
+      </c>
+      <c r="Y342">
+        <v>8</v>
+      </c>
+      <c r="Z342">
+        <v>6</v>
+      </c>
+      <c r="AA342">
+        <v>8</v>
+      </c>
+      <c r="AB342">
+        <v>3</v>
+      </c>
+      <c r="AC342">
+        <v>1</v>
+      </c>
+      <c r="AD342">
+        <v>3</v>
+      </c>
+      <c r="AE342">
+        <v>8</v>
+      </c>
+      <c r="AF342">
+        <v>2</v>
+      </c>
+      <c r="AG342">
+        <v>8</v>
+      </c>
+      <c r="AH342">
+        <v>7</v>
+      </c>
+      <c r="AI342">
+        <v>2</v>
+      </c>
+      <c r="AJ342">
+        <v>2</v>
+      </c>
+      <c r="AK342">
+        <v>5</v>
+      </c>
+      <c r="AL342">
+        <v>5</v>
+      </c>
+      <c r="AM342">
+        <v>5</v>
+      </c>
+      <c r="AN342">
+        <v>4</v>
+      </c>
+      <c r="AO342">
+        <v>4</v>
+      </c>
+      <c r="AP342">
+        <v>4</v>
+      </c>
+      <c r="AQ342">
+        <v>5</v>
+      </c>
+      <c r="AR342">
+        <v>2</v>
+      </c>
+      <c r="AS342">
+        <v>2</v>
+      </c>
+      <c r="AT342">
+        <v>2</v>
+      </c>
+      <c r="AU342">
+        <v>2</v>
+      </c>
+      <c r="AV342">
+        <v>2</v>
+      </c>
+      <c r="AW342">
+        <v>2</v>
+      </c>
+      <c r="AX342">
+        <v>3</v>
+      </c>
+      <c r="AY342">
+        <v>3</v>
+      </c>
+      <c r="AZ342">
+        <v>5</v>
+      </c>
+      <c r="BA342">
+        <v>1</v>
+      </c>
+      <c r="BB342">
+        <v>2</v>
+      </c>
+      <c r="BC342">
+        <v>4</v>
+      </c>
+      <c r="BD342">
+        <v>2</v>
+      </c>
+      <c r="BE342">
+        <v>2</v>
+      </c>
+      <c r="BF342">
+        <v>5</v>
+      </c>
+      <c r="BG342">
+        <v>2</v>
+      </c>
+      <c r="BH342">
+        <v>2</v>
+      </c>
+      <c r="BI342">
+        <v>5</v>
+      </c>
+      <c r="BJ342">
+        <v>4</v>
+      </c>
+      <c r="BK342">
+        <v>5</v>
+      </c>
+      <c r="BL342">
+        <v>4</v>
+      </c>
+      <c r="BM342">
+        <v>5</v>
+      </c>
+      <c r="BN342">
+        <v>5</v>
+      </c>
+      <c r="BO342">
+        <v>5</v>
+      </c>
+      <c r="BP342" t="s">
+        <v>218</v>
+      </c>
+      <c r="BQ342" t="s">
+        <v>222</v>
+      </c>
+      <c r="BR342" t="s">
+        <v>220</v>
+      </c>
+      <c r="BS342" t="s">
+        <v>225</v>
+      </c>
+      <c r="BT342" t="s">
+        <v>117</v>
+      </c>
+      <c r="BU342" t="s">
+        <v>218</v>
+      </c>
+      <c r="BV342">
+        <v>2</v>
+      </c>
+      <c r="BW342">
+        <v>4</v>
+      </c>
+      <c r="CE342">
+        <v>151</v>
+      </c>
+      <c r="CF342">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="343" spans="1:84" x14ac:dyDescent="0.2">
+      <c r="A343" t="s">
+        <v>805</v>
+      </c>
+      <c r="C343" t="s">
+        <v>806</v>
+      </c>
+      <c r="H343">
+        <v>3</v>
+      </c>
+      <c r="I343">
+        <v>9</v>
+      </c>
+      <c r="J343">
+        <v>8</v>
+      </c>
+      <c r="K343">
+        <v>10</v>
+      </c>
+      <c r="L343">
+        <v>7</v>
+      </c>
+      <c r="M343">
+        <v>8</v>
+      </c>
+      <c r="N343">
+        <v>3</v>
+      </c>
+      <c r="O343">
+        <v>7</v>
+      </c>
+      <c r="P343">
+        <v>8</v>
+      </c>
+      <c r="Q343">
+        <v>3</v>
+      </c>
+      <c r="R343">
+        <v>8</v>
+      </c>
+      <c r="S343">
+        <v>8</v>
+      </c>
+      <c r="T343">
+        <v>6</v>
+      </c>
+      <c r="U343">
+        <v>8</v>
+      </c>
+      <c r="V343">
+        <v>1</v>
+      </c>
+      <c r="W343">
+        <v>9</v>
+      </c>
+      <c r="X343">
+        <v>8</v>
+      </c>
+      <c r="Y343">
+        <v>8</v>
+      </c>
+      <c r="Z343">
+        <v>7</v>
+      </c>
+      <c r="AA343">
+        <v>9</v>
+      </c>
+      <c r="AB343">
+        <v>7</v>
+      </c>
+      <c r="AC343">
+        <v>8</v>
+      </c>
+      <c r="AD343">
+        <v>7</v>
+      </c>
+      <c r="AE343">
+        <v>9</v>
+      </c>
+      <c r="AF343">
+        <v>7</v>
+      </c>
+      <c r="AG343">
+        <v>7</v>
+      </c>
+      <c r="AH343">
+        <v>8</v>
+      </c>
+      <c r="AI343">
+        <v>5</v>
+      </c>
+      <c r="AJ343">
+        <v>5</v>
+      </c>
+      <c r="AK343">
+        <v>5</v>
+      </c>
+      <c r="AL343">
+        <v>5</v>
+      </c>
+      <c r="AM343">
+        <v>6</v>
+      </c>
+      <c r="AN343">
+        <v>4</v>
+      </c>
+      <c r="AO343">
+        <v>5</v>
+      </c>
+      <c r="AP343">
+        <v>4</v>
+      </c>
+      <c r="AQ343">
+        <v>6</v>
+      </c>
+      <c r="AR343">
+        <v>4</v>
+      </c>
+      <c r="AS343">
+        <v>6</v>
+      </c>
+      <c r="AT343">
+        <v>5</v>
+      </c>
+      <c r="AU343">
+        <v>5</v>
+      </c>
+      <c r="AV343">
+        <v>5</v>
+      </c>
+      <c r="AW343">
+        <v>5</v>
+      </c>
+      <c r="AX343">
+        <v>5</v>
+      </c>
+      <c r="AY343">
+        <v>4</v>
+      </c>
+      <c r="AZ343">
+        <v>5</v>
+      </c>
+      <c r="BA343">
+        <v>1</v>
+      </c>
+      <c r="BB343">
+        <v>2</v>
+      </c>
+      <c r="BC343">
+        <v>6</v>
+      </c>
+      <c r="BD343">
+        <v>6</v>
+      </c>
+      <c r="BE343">
+        <v>5</v>
+      </c>
+      <c r="BF343">
+        <v>5</v>
+      </c>
+      <c r="BG343">
+        <v>6</v>
+      </c>
+      <c r="BH343">
+        <v>4</v>
+      </c>
+      <c r="BI343">
+        <v>4</v>
+      </c>
+      <c r="BJ343">
+        <v>2</v>
+      </c>
+      <c r="BK343">
+        <v>5</v>
+      </c>
+      <c r="BL343">
+        <v>5</v>
+      </c>
+      <c r="BM343">
+        <v>5</v>
+      </c>
+      <c r="BN343">
+        <v>4</v>
+      </c>
+      <c r="BO343">
+        <v>5</v>
+      </c>
+      <c r="BP343" t="s">
+        <v>219</v>
+      </c>
+      <c r="BQ343" t="s">
+        <v>222</v>
+      </c>
+      <c r="BR343" t="s">
+        <v>225</v>
+      </c>
+      <c r="BS343" t="s">
+        <v>225</v>
+      </c>
+      <c r="BT343" t="s">
+        <v>116</v>
+      </c>
+      <c r="BU343" t="s">
+        <v>218</v>
+      </c>
+      <c r="BV343">
+        <v>2</v>
+      </c>
+      <c r="BW343">
+        <v>4</v>
+      </c>
+      <c r="CE343">
+        <v>191</v>
+      </c>
+      <c r="CF343">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="344" spans="1:84" x14ac:dyDescent="0.2">
+      <c r="A344" s="22">
+        <v>45661.830046296294</v>
+      </c>
+      <c r="B344" t="s">
+        <v>807</v>
+      </c>
+      <c r="C344" t="s">
+        <v>808</v>
+      </c>
+      <c r="H344">
+        <v>5</v>
+      </c>
+      <c r="I344">
+        <v>9</v>
+      </c>
+      <c r="J344">
+        <v>3</v>
+      </c>
+      <c r="K344">
+        <v>10</v>
+      </c>
+      <c r="L344">
+        <v>2</v>
+      </c>
+      <c r="M344">
+        <v>7</v>
+      </c>
+      <c r="N344">
+        <v>2</v>
+      </c>
+      <c r="O344">
+        <v>8</v>
+      </c>
+      <c r="P344">
+        <v>9</v>
+      </c>
+      <c r="Q344">
+        <v>8</v>
+      </c>
+      <c r="R344">
+        <v>7</v>
+      </c>
+      <c r="S344">
+        <v>9</v>
+      </c>
+      <c r="T344">
+        <v>4</v>
+      </c>
+      <c r="U344">
+        <v>3</v>
+      </c>
+      <c r="V344">
+        <v>1</v>
+      </c>
+      <c r="W344">
+        <v>8</v>
+      </c>
+      <c r="X344">
+        <v>8</v>
+      </c>
+      <c r="Y344">
+        <v>2</v>
+      </c>
+      <c r="Z344">
+        <v>2</v>
+      </c>
+      <c r="AA344">
+        <v>9</v>
+      </c>
+      <c r="AB344">
+        <v>1</v>
+      </c>
+      <c r="AC344">
+        <v>1</v>
+      </c>
+      <c r="AD344">
+        <v>1</v>
+      </c>
+      <c r="AE344">
+        <v>9</v>
+      </c>
+      <c r="AF344">
+        <v>8</v>
+      </c>
+      <c r="AG344">
+        <v>9</v>
+      </c>
+      <c r="AH344">
+        <v>2</v>
+      </c>
+      <c r="AI344">
+        <v>1</v>
+      </c>
+      <c r="AJ344">
+        <v>1</v>
+      </c>
+      <c r="AK344">
+        <v>6</v>
+      </c>
+      <c r="AL344">
+        <v>4</v>
+      </c>
+      <c r="AM344">
+        <v>2</v>
+      </c>
+      <c r="AN344">
+        <v>5</v>
+      </c>
+      <c r="AO344">
+        <v>4</v>
+      </c>
+      <c r="AP344">
+        <v>3</v>
+      </c>
+      <c r="AQ344">
+        <v>4</v>
+      </c>
+      <c r="AR344">
+        <v>2</v>
+      </c>
+      <c r="AS344">
+        <v>1</v>
+      </c>
+      <c r="AT344">
+        <v>2</v>
+      </c>
+      <c r="AU344">
+        <v>2</v>
+      </c>
+      <c r="AV344">
+        <v>1</v>
+      </c>
+      <c r="AW344">
+        <v>5</v>
+      </c>
+      <c r="AX344">
+        <v>5</v>
+      </c>
+      <c r="AY344">
+        <v>1</v>
+      </c>
+      <c r="AZ344">
+        <v>1</v>
+      </c>
+      <c r="BA344">
+        <v>2</v>
+      </c>
+      <c r="BB344">
+        <v>2</v>
+      </c>
+      <c r="BC344">
+        <v>1</v>
+      </c>
+      <c r="BD344">
+        <v>2</v>
+      </c>
+      <c r="BE344">
+        <v>2</v>
+      </c>
+      <c r="BF344">
+        <v>5</v>
+      </c>
+      <c r="BG344">
+        <v>2</v>
+      </c>
+      <c r="BH344">
+        <v>2</v>
+      </c>
+      <c r="BI344">
+        <v>5</v>
+      </c>
+      <c r="BJ344">
+        <v>5</v>
+      </c>
+      <c r="BK344">
+        <v>4</v>
+      </c>
+      <c r="BL344">
+        <v>5</v>
+      </c>
+      <c r="BM344">
+        <v>4</v>
+      </c>
+      <c r="BN344">
+        <v>5</v>
+      </c>
+      <c r="BO344">
+        <v>2</v>
+      </c>
+      <c r="BP344" t="s">
+        <v>218</v>
+      </c>
+      <c r="BQ344" t="s">
+        <v>220</v>
+      </c>
+      <c r="BR344" t="s">
+        <v>225</v>
+      </c>
+      <c r="BS344" t="s">
+        <v>225</v>
+      </c>
+      <c r="BT344" t="s">
+        <v>117</v>
+      </c>
+      <c r="BU344" t="s">
+        <v>218</v>
+      </c>
+      <c r="BV344">
+        <v>1</v>
+      </c>
+      <c r="BW344">
+        <v>1</v>
+      </c>
+      <c r="CE344">
+        <v>147</v>
+      </c>
+      <c r="CF344">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="345" spans="1:84" x14ac:dyDescent="0.2">
+      <c r="A345" s="22">
+        <v>45692.620740740742</v>
+      </c>
+      <c r="B345" t="s">
+        <v>809</v>
+      </c>
+      <c r="C345" t="s">
+        <v>810</v>
+      </c>
+      <c r="H345">
+        <v>5</v>
+      </c>
+      <c r="I345">
+        <v>3</v>
+      </c>
+      <c r="J345">
+        <v>1</v>
+      </c>
+      <c r="K345">
+        <v>10</v>
+      </c>
+      <c r="L345">
+        <v>1</v>
+      </c>
+      <c r="M345">
+        <v>1</v>
+      </c>
+      <c r="N345">
+        <v>1</v>
+      </c>
+      <c r="O345">
+        <v>4</v>
+      </c>
+      <c r="P345">
+        <v>6</v>
+      </c>
+      <c r="Q345">
+        <v>2</v>
+      </c>
+      <c r="R345">
+        <v>9</v>
+      </c>
+      <c r="S345">
+        <v>2</v>
+      </c>
+      <c r="T345">
+        <v>3</v>
+      </c>
+      <c r="U345">
+        <v>2</v>
+      </c>
+      <c r="V345">
+        <v>5</v>
+      </c>
+      <c r="W345">
+        <v>1</v>
+      </c>
+      <c r="X345">
+        <v>9</v>
+      </c>
+      <c r="Y345">
+        <v>2</v>
+      </c>
+      <c r="Z345">
+        <v>5</v>
+      </c>
+      <c r="AA345">
+        <v>2</v>
+      </c>
+      <c r="AB345">
+        <v>5</v>
+      </c>
+      <c r="AC345">
+        <v>2</v>
+      </c>
+      <c r="AD345">
+        <v>1</v>
+      </c>
+      <c r="AE345">
+        <v>2</v>
+      </c>
+      <c r="AF345">
+        <v>3</v>
+      </c>
+      <c r="AG345">
+        <v>4</v>
+      </c>
+      <c r="AH345">
+        <v>5</v>
+      </c>
+      <c r="AI345">
+        <v>3</v>
+      </c>
+      <c r="AJ345">
+        <v>3</v>
+      </c>
+      <c r="AK345">
+        <v>3</v>
+      </c>
+      <c r="AL345">
+        <v>5</v>
+      </c>
+      <c r="AM345">
+        <v>4</v>
+      </c>
+      <c r="AN345">
+        <v>4</v>
+      </c>
+      <c r="AO345">
+        <v>3</v>
+      </c>
+      <c r="AP345">
+        <v>3</v>
+      </c>
+      <c r="AQ345">
+        <v>3</v>
+      </c>
+      <c r="AR345">
+        <v>1</v>
+      </c>
+      <c r="AS345">
+        <v>2</v>
+      </c>
+      <c r="AT345">
+        <v>3</v>
+      </c>
+      <c r="AU345">
+        <v>1</v>
+      </c>
+      <c r="AV345">
+        <v>3</v>
+      </c>
+      <c r="AW345">
+        <v>2</v>
+      </c>
+      <c r="AX345">
+        <v>1</v>
+      </c>
+      <c r="AY345">
+        <v>1</v>
+      </c>
+      <c r="AZ345">
+        <v>5</v>
+      </c>
+      <c r="BA345">
+        <v>5</v>
+      </c>
+      <c r="BB345">
+        <v>2</v>
+      </c>
+      <c r="BC345">
+        <v>3</v>
+      </c>
+      <c r="BD345">
+        <v>2</v>
+      </c>
+      <c r="BE345">
+        <v>3</v>
+      </c>
+      <c r="BF345">
+        <v>3</v>
+      </c>
+      <c r="BG345">
+        <v>4</v>
+      </c>
+      <c r="BH345">
+        <v>4</v>
+      </c>
+      <c r="BI345">
+        <v>4</v>
+      </c>
+      <c r="BJ345">
+        <v>4</v>
+      </c>
+      <c r="BK345">
+        <v>3</v>
+      </c>
+      <c r="BL345">
+        <v>3</v>
+      </c>
+      <c r="BM345">
+        <v>3</v>
+      </c>
+      <c r="BN345">
+        <v>3</v>
+      </c>
+      <c r="BO345">
+        <v>2</v>
+      </c>
+      <c r="BP345" t="s">
+        <v>218</v>
+      </c>
+      <c r="BQ345" t="s">
+        <v>221</v>
+      </c>
+      <c r="BR345" t="s">
+        <v>221</v>
+      </c>
+      <c r="BS345" t="s">
+        <v>221</v>
+      </c>
+      <c r="BT345" t="s">
+        <v>117</v>
+      </c>
+      <c r="BU345" t="s">
+        <v>218</v>
+      </c>
+      <c r="BV345">
+        <v>1</v>
+      </c>
+      <c r="BW345">
+        <v>1</v>
+      </c>
+      <c r="CE345">
+        <v>96</v>
+      </c>
+      <c r="CF345">
+        <v>98</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
